--- a/Reports/Room 3/Ledger 2.xlsx
+++ b/Reports/Room 3/Ledger 2.xlsx
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">A further 7 deposits totalling $375.00 were received for cleaning, a service charged separately from rent. They are excluded from this ledger and nothing is outstanding on that account.</t>
+          <t xml:space="preserve">A further 7 deposits totalling $375.00 were received for cleaning, a service charged separately from rent, against $35.00 paid out for that service in the same period — $340.00 net. Cleaning is excluded from this rent ledger and nothing is outstanding on that account; both sides are set out under CLEANING below.</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOTAL</t>
+          <t xml:space="preserve">TOTAL RECEIVED</t>
         </is>
       </c>
       <c r="C12" s="4">
@@ -2344,14 +2344,142 @@
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Note</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">These deposits are payments for cleaning, a service charged separately from the rent. They are excluded from the rent ledger on the first tab and no amount remains outstanding on this account.</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID FOR CLEANING</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Money spent on the service over the same period</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paid to</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amount</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reference</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Description on statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>46230</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diana Cleaning Alabama $25</t>
+        </is>
+      </c>
+      <c r="C16" s="3">
+        <v>35</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USBCsRBsqPnM</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZELLE INSTANT PMT TO Diana Cleaning Alabama $25 USBCsRBsqPnM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOTAL PAID</t>
+        </is>
+      </c>
+      <c r="C17" s="4">
+        <f>SUM(C16:C16)</f>
+        <v>35.00</v>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NET (received less paid)</t>
+        </is>
+      </c>
+      <c r="C19" s="4">
+        <f>C12-C17</f>
+        <v>340.00</v>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Note 1</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deposits above are payments received from the tenants for cleaning, a service charged separately from the rent. They are excluded from the rent ledger on the first tab and no amount remains outstanding on this account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Note 2</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amounts paid are the outgoing transfers for cleaning found in the same bank export. Both sections cover July 1, 2025 through September 3, 2026.</t>
         </is>
       </c>
     </row>

--- a/Reports/Room 3/Ledger 2.xlsx
+++ b/Reports/Room 3/Ledger 2.xlsx
@@ -158,7 +158,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">July 1, 2025 through September 3, 2026</t>
+          <t xml:space="preserve">July 1, 2025 through September 8, 2026</t>
         </is>
       </c>
     </row>
@@ -182,7 +182,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">September 3, 2026</t>
+          <t xml:space="preserve">September 8, 2026</t>
         </is>
       </c>
     </row>
@@ -2000,90 +2000,107 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="8" t="inlineStr">
+      <c r="A104" s="5">
+        <v>46273</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rent due — week of September 8, 2026</t>
+        </is>
+      </c>
+      <c r="C104" s="3">
+        <v>425</v>
+      </c>
+      <c r="E104" s="3">
+        <f>E103+C104-D104</f>
+        <v>10925.00</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">TOTALS</t>
         </is>
       </c>
-      <c r="C104" s="4">
-        <f>SUM(C9:C103)</f>
-        <v>26350.00</v>
-      </c>
-      <c r="D104" s="4">
-        <f>SUM(D9:D103)</f>
+      <c r="C105" s="4">
+        <f>SUM(C9:C104)</f>
+        <v>26775.00</v>
+      </c>
+      <c r="D105" s="4">
+        <f>SUM(D9:D104)</f>
         <v>15850.00</v>
       </c>
-      <c r="E104" s="4">
-        <f>C104-D104</f>
-        <v>10500.00</v>
-      </c>
-      <c r="F104" s="8" t="inlineStr">
+      <c r="E105" s="4">
+        <f>C105-D105</f>
+        <v>10925.00</v>
+      </c>
+      <c r="F105" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
-    <row r="105"/>
-    <row r="106">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Note 1</t>
-        </is>
-      </c>
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rent accrues at $425.00 per week, one charge every seven days beginning July 1, 2025. Only whole weeks already fallen due are charged — a part week is never accrued, so no proration appears in this ledger.</t>
-        </is>
-      </c>
-    </row>
+    <row r="106"/>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Note 2</t>
+          <t xml:space="preserve">Note 1</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Payments are the actual Zelle deposits credited to U.S. Bank checking account ····8247, taken from the export Checking - 8247_07-01-2025_09-06-2026.csv. Each row corresponds to one row of that export; nothing is estimated.</t>
+          <t xml:space="preserve">Rent accrues at $425.00 per week, one charge every seven days beginning July 1, 2025. Only whole weeks already fallen due are charged — a part week is never accrued, so no proration appears in this ledger.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Note 3</t>
+          <t xml:space="preserve">Note 2</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Balance Due is a running total: charges less payments as at each row. A negative figure means payments had, at that date, run ahead of the rent accrued.</t>
+          <t xml:space="preserve">Payments are the actual Zelle deposits credited to U.S. Bank checking account ····8247, taken from the export Checking - 8247_07-01-2025_09-06-2026.csv. Each row corresponds to one row of that export; nothing is estimated.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Note 4</t>
+          <t xml:space="preserve">Note 3</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">A further 7 deposits totalling $375.00 were received for cleaning, a service charged separately from rent, against $35.00 paid out for that service in the same period — $340.00 net. Cleaning is excluded from this rent ledger and nothing is outstanding on that account; both sides are set out under CLEANING below.</t>
+          <t xml:space="preserve">Balance Due is a running total: charges less payments as at each row. A negative figure means payments had, at that date, run ahead of the rent accrued.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Note 4</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A further 7 deposits totalling $375.00 were received for cleaning, a service charged separately from rent, against $35.00 paid out for that service in the same period — $340.00 net. Cleaning is excluded from this rent ledger and nothing is outstanding on that account; both sides are set out under CLEANING below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Note 5</t>
         </is>
       </c>
-      <c r="B110" s="7" t="inlineStr">
+      <c r="B111" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">This ledger is an informational compilation prepared from the bank export named above; it does not replace the primary bank statements.</t>
         </is>
@@ -2479,7 +2496,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amounts paid are the outgoing transfers for cleaning found in the same bank export. Both sections cover July 1, 2025 through September 3, 2026.</t>
+          <t xml:space="preserve">Amounts paid are the outgoing transfers for cleaning found in the same bank export. Both sections cover July 1, 2025 through September 8, 2026.</t>
         </is>
       </c>
     </row>
